--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487661_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487661_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1506</v>
+        <v>7.2594</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0487</v>
+        <v>6.1303</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1019</v>
+        <v>1.1292</v>
       </c>
       <c r="G2" t="n">
         <v>3.4108</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1875</v>
+        <v>0.2964</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.35</v>
+        <v>-0.2684</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5375</v>
+        <v>0.5648</v>
       </c>
       <c r="V2" t="n">
         <v>1.2239</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2132</v>
+        <v>3.6162</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7813</v>
+        <v>3.1842</v>
       </c>
       <c r="F3" t="n">
         <v>0.4319</v>
@@ -688,10 +688,10 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0606</v>
+        <v>0.4635</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5317</v>
+        <v>-0.1287</v>
       </c>
       <c r="U3" t="n">
         <v>0.5921999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3251</v>
+        <v>1.5637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.863</v>
+        <v>0.1834</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4621</v>
+        <v>1.3803</v>
       </c>
       <c r="G4" t="n">
         <v>0.0857</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4618</v>
+        <v>0.7004</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1541</v>
+        <v>0.4744</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3078</v>
+        <v>0.226</v>
       </c>
       <c r="V4" t="n">
         <v>1.5537</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0647</v>
+        <v>0.9495</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4775</v>
+        <v>-2.4565</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5422</v>
+        <v>3.4059</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5508</v>
@@ -844,13 +844,13 @@
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2961</v>
+        <v>0.1809</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1683</v>
+        <v>-0.1472</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4644</v>
+        <v>0.3281</v>
       </c>
       <c r="V5" t="n">
         <v>1.3194</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7884</v>
+        <v>0.885</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-0.9352</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7656</v>
+        <v>1.8201</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0057</v>
@@ -922,13 +922,13 @@
         <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0119</v>
+        <v>0.0847</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1806</v>
+        <v>-0.1385</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1687</v>
+        <v>0.2232</v>
       </c>
       <c r="V6" t="n">
         <v>1.8358</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8729</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.4648</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2474</v>
+        <v>-0.1657</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9274</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1395</v>
+        <v>0.1029</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1211</v>
+        <v>0.0395</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0184</v>
+        <v>0.0634</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0793</v>
+        <v>-0.6701</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4103</v>
+        <v>-0.0284</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.669</v>
+        <v>-0.6417</v>
       </c>
       <c r="G8" t="n">
         <v>0.489</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7221</v>
+        <v>-0.3129</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>0.0791</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4192</v>
+        <v>-0.392</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8462</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3689</v>
+        <v>-1.1176</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1886</v>
+        <v>-0.1281</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1803</v>
+        <v>-0.9895</v>
       </c>
       <c r="G9" t="n">
         <v>0.1461</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1151</v>
+        <v>0.1363</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1694</v>
+        <v>-0.1088</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0543</v>
+        <v>0.2451</v>
       </c>
       <c r="V9" t="n">
         <v>-1.788</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4752</v>
+        <v>-1.1777</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9791</v>
+        <v>-1.5181</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5039</v>
+        <v>0.3404</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1475</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3277</v>
+        <v>-0.0303</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.424</v>
+        <v>0.037</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9744</v>
+        <v>-3.3923</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0696</v>
+        <v>-3.4875</v>
       </c>
       <c r="F11" t="n">
         <v>0.09520000000000001</v>
@@ -1312,10 +1312,10 @@
         <v>2.5224</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.116</v>
+        <v>-0.5339</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1384</v>
+        <v>-0.5563</v>
       </c>
       <c r="U11" t="n">
         <v>0.0225</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.771299999999999</v>
+        <v>7.285599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.034899999999999</v>
+        <v>0.4793000000000007</v>
       </c>
       <c r="F12" t="n">
         <v>6.8061</v>
@@ -1390,10 +1390,10 @@
         <v>17.4629</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4262999999999998</v>
+        <v>1.088</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2322</v>
+        <v>-0.7179</v>
       </c>
       <c r="U12" t="n">
         <v>1.806</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9659</v>
+        <v>6.3085</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4957</v>
+        <v>6.5958</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5298</v>
+        <v>-0.2873</v>
       </c>
       <c r="G13" t="n">
         <v>2.8892</v>
@@ -1468,13 +1468,13 @@
         <v>2.5224</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1696</v>
+        <v>0.173</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3017</v>
+        <v>-0.2016</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1321</v>
+        <v>0.3746</v>
       </c>
       <c r="V13" t="n">
         <v>0.7239</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6166</v>
+        <v>1.2789</v>
       </c>
       <c r="E14" t="n">
-        <v>3.014</v>
+        <v>0.6538</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3974</v>
+        <v>0.6251</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3439</v>
+        <v>2.5556</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8939</v>
+        <v>1.5818</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.55</v>
+        <v>0.9738</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6003</v>
+        <v>2.7694</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3161</v>
+        <v>2.7188</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2842</v>
+        <v>0.0507</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2564</v>
+        <v>-0.2138</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4222</v>
+        <v>-1.137</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8342000000000001</v>
+        <v>0.9231</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7164</v>
+        <v>3.2985</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5787</v>
+        <v>-0.3185</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1377</v>
+        <v>-0.429</v>
       </c>
       <c r="U14" t="n">
-        <v>1.441</v>
+        <v>0.1105</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.112</v>
+        <v>-1.3463</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1865</v>
+        <v>1.2239</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2985</v>
+        <v>-2.5701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5965</v>
+        <v>0.3787</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0532</v>
+        <v>1.2122</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5433</v>
+        <v>-0.8335</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5556</v>
+        <v>0.3439</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5818</v>
+        <v>0.8939</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9738</v>
+        <v>-0.55</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7694</v>
+        <v>3.6003</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7188</v>
+        <v>3.3161</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0507</v>
+        <v>0.2842</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2138</v>
+        <v>-3.2564</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.137</v>
+        <v>-2.4222</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9231</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2985</v>
+        <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0009</v>
+        <v>1.3408</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0296</v>
+        <v>0.3359</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0287</v>
+        <v>1.005</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3463</v>
+        <v>-1.112</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0.1865</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5701</v>
+        <v>-1.2985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5848</v>
+        <v>0.0919</v>
       </c>
       <c r="E16" t="n">
-        <v>0.463</v>
+        <v>-2.3101</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0478</v>
+        <v>2.402</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1301</v>
+        <v>-1.1861</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3098</v>
+        <v>1.3792</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1796</v>
+        <v>-2.5653</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6324</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0412</v>
+        <v>2.7105</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5911999999999999</v>
+        <v>-2.1315</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7625</v>
+        <v>-1.7652</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.351</v>
+        <v>-1.3314</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4115</v>
+        <v>-0.4338</v>
       </c>
       <c r="P16" t="n">
-        <v>0.194</v>
+        <v>1.5523</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>0.194</v>
+        <v>3.4926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6487000000000001</v>
+        <v>0.3855</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1694</v>
+        <v>-0.5712</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4794</v>
+        <v>0.9567</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.2052</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0108</v>
+        <v>-2.4334</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1595</v>
+        <v>2.2283</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1861</v>
+        <v>-0.1083</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3792</v>
+        <v>0.7909</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5653</v>
+        <v>-0.8992</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5790999999999999</v>
+        <v>1.535</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7105</v>
+        <v>2.1338</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1315</v>
+        <v>-0.5989</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7652</v>
+        <v>-1.6433</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3314</v>
+        <v>-1.3429</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4338</v>
+        <v>-0.3004</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>3.4926</v>
+        <v>3.6866</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5576</v>
+        <v>0.4733</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2719</v>
+        <v>-0.3982</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="V17" t="n">
+        <v>-1.3463</v>
+      </c>
+      <c r="W17" t="n">
         <v>-0.6597</v>
       </c>
-      <c r="W17" t="n">
-        <v>-0.3776</v>
-      </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>-0.6866</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2114</v>
+        <v>-0.3029</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2788</v>
+        <v>0.6632</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0675</v>
+        <v>-0.9661</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7938</v>
+        <v>-0.1301</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6788999999999999</v>
+        <v>-0.3098</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4726</v>
+        <v>0.1796</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8874</v>
+        <v>0.6324</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3924</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5049</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6812</v>
+        <v>-0.7625</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7135</v>
+        <v>-0.351</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9677</v>
+        <v>-0.4115</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7164</v>
+        <v>0.194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0496</v>
+        <v>-0.3668</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1233</v>
+        <v>0.0308</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0738</v>
+        <v>-0.3976</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2134</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.3194</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2484</v>
+        <v>-1.515</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2342</v>
+        <v>-1.8794</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9858</v>
+        <v>0.3645</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1083</v>
+        <v>-0.7938</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7909</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8992</v>
+        <v>-1.4726</v>
       </c>
       <c r="J19" t="n">
-        <v>1.535</v>
+        <v>0.8874</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1338</v>
+        <v>1.3924</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5989</v>
+        <v>-0.5049</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6433</v>
+        <v>-1.6812</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3429</v>
+        <v>-0.7135</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3004</v>
+        <v>-0.9677</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6866</v>
+        <v>2.7164</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.57</v>
+        <v>-0.254</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.199</v>
+        <v>-0.4773</v>
       </c>
       <c r="U19" t="n">
-        <v>0.629</v>
+        <v>0.2232</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3463</v>
+        <v>-2.2134</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>-1.3194</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6866</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6992</v>
+        <v>-5.1113</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7555</v>
+        <v>-5.0558</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0562</v>
+        <v>-0.0556</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9763</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3816</v>
+        <v>-0.0306</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3163</v>
+        <v>0.016</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0653</v>
+        <v>-0.0465</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.3552</v>
+        <v>-6.0277</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5528</v>
+        <v>-4.2525</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8024</v>
+        <v>-1.7752</v>
       </c>
       <c r="G21" t="n">
         <v>-4.6258</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6368</v>
+        <v>-0.3093</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4116</v>
+        <v>-0.1113</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2252</v>
+        <v>-0.1979</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1224</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.771300000000002</v>
+        <v>-5.1041</v>
       </c>
       <c r="E22" t="n">
         <v>-6.8062</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0349</v>
+        <v>1.7022</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0317</v>
+        <v>-3.031699999999999</v>
       </c>
       <c r="H22" t="n">
         <v>-0.3624999999999998</v>
@@ -2170,13 +2170,13 @@
         <v>20.3732</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4263000000000001</v>
+        <v>1.0934</v>
       </c>
       <c r="T22" t="n">
         <v>-1.8059</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2319</v>
+        <v>2.8995</v>
       </c>
       <c r="V22" t="n">
         <v>-6.0762</v>
